--- a/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARKAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="92">
   <si>
     <t>ARKAY</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -768,8 +769,11 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,21 +816,21 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>2776800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3211800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6605900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3132400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -848,8 +852,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,21 +899,21 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>2358100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2546100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4880100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2316500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -928,8 +935,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -972,21 +982,21 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>418700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>665700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1725700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>815900</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,8 +1018,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,8 +1051,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1082,21 +1096,21 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3">
         <v>78600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>71300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>144700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>71600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1118,8 +1132,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1198,8 +1215,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1242,21 +1262,21 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>78600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>101200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,8 +1298,11 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1322,8 +1345,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1340,8 +1363,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
@@ -1358,8 +1381,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1385,8 +1411,9 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1429,21 +1456,21 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>2756800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2864900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5574300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2661500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1465,8 +1492,11 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1509,21 +1539,21 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>19900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>346900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1031500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>470900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,8 +1575,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,8 +1608,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1619,21 +1653,21 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-35400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-16300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9800</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1655,8 +1689,11 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1699,12 +1736,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>767600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,8 +1772,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1779,8 +1819,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1797,8 +1837,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1815,8 +1855,11 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1859,21 +1902,21 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>-15500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>325300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1015200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>461100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,8 +1938,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1939,21 +1985,21 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>-25500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>82100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>218700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>103100</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1975,8 +2021,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2055,8 +2104,11 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2099,21 +2151,21 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>10000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>243200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>796500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>358100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2135,8 +2187,11 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2179,21 +2234,21 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>-5500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>242100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>788900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>357000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2215,8 +2270,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2295,8 +2353,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2339,8 +2400,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2357,8 +2418,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
@@ -2375,8 +2436,11 @@
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2455,8 +2519,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2535,8 +2602,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2579,21 +2649,21 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>35400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>16300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9800</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,8 +2685,11 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2659,21 +2732,21 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>-5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>242100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>788900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>357000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2768,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2775,8 +2851,11 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2819,21 +2898,21 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>-5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>242100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>788900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>357000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,70 +2934,73 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3022,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2970,8 +3055,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3000,53 +3086,54 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1675900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1994600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2569000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2291400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1539600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1208400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2084100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2225100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2243700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2498700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2260400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2011000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1818800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2082800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,11 +3146,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -3080,8 +3167,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3124,8 +3214,8 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -3139,11 +3229,11 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
@@ -3160,53 +3250,56 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2059300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1745900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1932400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2059900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1990900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1671000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1910600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1998300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1920400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1738700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1796100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1954100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2041500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,11 +3312,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
@@ -3240,53 +3333,56 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1599300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1497800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1340800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1535800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1537300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1553200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1395600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1552500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1458300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1430600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1335200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1425700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1505500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1597100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,11 +3395,11 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
@@ -3320,53 +3416,56 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E45" s="3">
         <v>25300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>57600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3382,8 +3481,8 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3400,53 +3499,56 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5482800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5576800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5665100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5784300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5177900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4773000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5171300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5736100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5713100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5860400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5369700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5246600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5325300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5779000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,11 +3561,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3480,53 +3582,56 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E47" s="3">
         <v>47800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>63800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>63200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>74700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>71800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>72000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>76400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>79300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,11 +3644,11 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3560,53 +3665,56 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4486200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4527000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4620200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4532400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4582500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4396900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4376200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4165700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4057600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4041400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4122900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3634600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3672500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3657100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3619,11 +3727,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3640,53 +3748,56 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5631000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5753300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5837700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5900500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5938900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5719800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5604100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5958100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5818100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5897100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5994300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5088900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5186700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5167300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,11 +3810,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3720,8 +3831,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3800,8 +3914,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3880,53 +3997,56 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>322200</v>
+      </c>
+      <c r="E52" s="3">
         <v>327700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>86900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>342600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>371100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>343700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>78700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>287800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>315000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>274000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>248700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>279500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>260800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3939,11 +4059,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -3960,8 +4080,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4040,53 +4163,56 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16191400</v>
+      </c>
+      <c r="E54" s="3">
         <v>16396500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16725400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16775800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16342900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15458300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15745900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16346200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16169500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16309200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16046200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14465500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14755500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15122800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4099,11 +4225,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
+        <v>0</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
@@ -4120,8 +4246,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4150,8 +4279,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4180,53 +4310,54 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1246100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1228900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1140100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1039500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1098100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1185700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1111900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1107500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1193600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1152200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1145100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1001300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1089500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1285300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4239,11 +4370,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4260,53 +4391,56 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1560700</v>
+      </c>
+      <c r="E58" s="3">
         <v>536500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>887600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>166600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>172600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>187000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>904900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>965900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1313600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1345300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>598000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>702800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>720500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>712700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4319,11 +4453,11 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4340,53 +4474,56 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>804000</v>
+      </c>
+      <c r="E59" s="3">
         <v>715000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>206600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>677000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>627100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>591200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>182200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>644700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>568900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>582600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>194500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>628700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>615700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>626900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,11 +4536,11 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4420,53 +4557,56 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3610800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2480300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2653500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1883100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1897800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1963900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2573800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2718000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3076200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3080200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2298000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2332800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2425800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2624900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4479,11 +4619,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3">
+        <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
@@ -4500,53 +4640,56 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3319700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4391300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4464000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4826900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4279500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3966700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3809900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3948200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3255100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3271100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4127300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3127600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3221600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3205100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4580,53 +4723,56 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>447300</v>
+      </c>
+      <c r="E62" s="3">
         <v>426700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>448500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>437600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>508500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>466900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>472100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>478500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>476800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>443400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>459800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>439200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>468300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>497600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,11 +4785,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
@@ -4660,8 +4806,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4740,8 +4889,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4820,8 +4972,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4900,53 +5055,56 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8237500</v>
+      </c>
+      <c r="E66" s="3">
         <v>8163600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8468900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8067600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7593700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7256800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7710900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8034800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7700600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7693400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7805900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6642700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6926900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7124100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,11 +5117,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
@@ -4980,8 +5138,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5010,8 +5171,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5090,8 +5252,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5170,8 +5335,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5232,8 +5400,8 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-      <c r="W70" s="3" t="s">
-        <v>3</v>
+      <c r="W70" s="3">
+        <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5418,11 @@
       <c r="AB70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5330,53 +5501,56 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4780200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5079400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5136800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5251700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5239000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5043200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4785200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5169500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4846200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4977900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5014900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4831700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4854800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4963100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5389,11 +5563,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5410,8 +5584,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5490,8 +5667,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5570,8 +5750,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5650,53 +5833,56 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7746000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8021300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8034500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8472400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8495600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7963700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7791700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8035900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8205300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8349300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7961800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7779400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7786000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7955200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5709,11 +5895,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5730,8 +5916,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5810,70 +5999,73 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5895,8 +6087,11 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5939,21 +6134,21 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>-5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>242100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>788900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>357000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,8 +6170,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6005,53 +6203,54 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>234500</v>
+      </c>
+      <c r="E83" s="3">
         <v>220900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>226700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>210800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>210000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>182000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>179000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>178200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>155900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>163100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>166600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6061,14 +6260,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -6085,8 +6284,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6165,8 +6367,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6245,8 +6450,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6325,8 +6533,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6405,8 +6616,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6485,53 +6699,56 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>211400</v>
+      </c>
+      <c r="E89" s="3">
         <v>37200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>497800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>349600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>297100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>421400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>372500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>316100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>91700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>510700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>416000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>299100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>155400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6541,14 +6758,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6565,8 +6782,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6595,53 +6815,54 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-133100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-311100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-153700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-177300</v>
-      </c>
       <c r="H91" s="3">
+        <v>-178200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-95900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-336500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-186300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-182100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-106800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-296200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-150300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-147400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-96700</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -6657,8 +6878,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6675,8 +6896,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6755,8 +6979,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6835,53 +7062,56 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-141100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-163800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-186700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-130200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-192600</v>
-      </c>
       <c r="H94" s="3">
+        <v>-192500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-197300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-407900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-178500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-212200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-202800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-931800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-132300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-248900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-172800</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6891,14 +7121,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6915,8 +7145,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6945,53 +7178,54 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>330600</v>
+      </c>
+      <c r="E96" s="3">
         <v>27300</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>319400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>319100</v>
+      </c>
+      <c r="I96" s="3">
         <v>25600</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>12300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>279700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>5400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>11600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>276200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>5400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7025,8 +7259,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7105,8 +7342,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7185,8 +7425,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7265,53 +7508,56 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-371800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-385000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>524500</v>
       </c>
-      <c r="G100" s="3">
-        <v>68100</v>
-      </c>
       <c r="H100" s="3">
+        <v>69100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-820700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-337900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-334300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>397000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>571500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-40200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-314400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>353100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7321,14 +7567,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -7345,53 +7591,56 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E101" s="3">
         <v>26000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-36200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>33500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>17400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-29400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-38700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>32200</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7401,14 +7650,14 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -7425,53 +7674,56 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-528800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>275900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>753300</v>
       </c>
-      <c r="G102" s="3">
-        <v>226700</v>
-      </c>
       <c r="H102" s="3">
+        <v>227700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-967800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-110400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-237900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>292400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>160300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>247700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-274000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>353100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7481,14 +7733,14 @@
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -7503,6 +7755,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
